--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.4495908161853</v>
+        <v>5.435558507630112</v>
       </c>
       <c r="D2" t="n">
-        <v>60.52362036612006</v>
+        <v>9.835088309494509</v>
       </c>
       <c r="E2" t="n">
-        <v>10.33997079752525</v>
+        <v>1.680245254597852</v>
       </c>
       <c r="F2" t="n">
-        <v>16.20575749128326</v>
+        <v>2.63343559233353</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.77910788765179</v>
+        <v>7.276605031743416</v>
       </c>
       <c r="D3" t="n">
-        <v>38.32608279256076</v>
+        <v>6.227988453791124</v>
       </c>
       <c r="E3" t="n">
-        <v>10.33997079752525</v>
+        <v>1.680245254597852</v>
       </c>
       <c r="F3" t="n">
-        <v>16.20575749128326</v>
+        <v>2.63343559233353</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.37619165235391</v>
+        <v>2.82363114350751</v>
       </c>
       <c r="D4" t="n">
-        <v>49.29220988711661</v>
+        <v>8.009984106656448</v>
       </c>
       <c r="E4" t="n">
-        <v>10.33997079752525</v>
+        <v>1.680245254597852</v>
       </c>
       <c r="F4" t="n">
-        <v>16.20575749128326</v>
+        <v>2.63343559233353</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.8309390887728</v>
+        <v>3.87252760192558</v>
       </c>
       <c r="D5" t="n">
-        <v>16.636595229643</v>
+        <v>2.703446724816987</v>
       </c>
       <c r="E5" t="n">
-        <v>10.33997079752525</v>
+        <v>1.680245254597852</v>
       </c>
       <c r="F5" t="n">
-        <v>16.20575749128326</v>
+        <v>2.63343559233353</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
